--- a/Dokumentation.xlsx
+++ b/Dokumentation.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20401"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF05D14-616C-48BE-A974-6685EB7A7A5E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C7948D-C147-4174-925D-2BD46F6A681E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="570">
   <si>
     <t>Name</t>
   </si>
@@ -992,12 +992,6 @@
   </si>
   <si>
     <t>Spielt eine Sonderansage ab</t>
-  </si>
-  <si>
-    <t>nuntius_printer_progressbarAnim</t>
-  </si>
-  <si>
-    <t>Animationsvariable für den Fortschrittsbalken</t>
   </si>
   <si>
     <t>nuntius_printer_autoOpenConfirmNextTripPage</t>
@@ -1744,12 +1738,81 @@
   <si>
     <t>Aktualisiert die Messung des Haltestellenabstandes im Sekundenabstand</t>
   </si>
+  <si>
+    <t>nuntius_printer_pleaseWaitReason</t>
+  </si>
+  <si>
+    <t>nuntius_printer_pleaseWaitDuration</t>
+  </si>
+  <si>
+    <t>nuntius_printer_targetPage</t>
+  </si>
+  <si>
+    <t>Wartezeit-Dauer in Sekunden</t>
+  </si>
+  <si>
+    <t>Timer für die Wartezeit. "Wie lange wurde bereits gewartet?"</t>
+  </si>
+  <si>
+    <t>Ziel-Page nach Ablauf der Wartezeit</t>
+  </si>
+  <si>
+    <t>Enum-Wert für den Grund der Wartezeit, die gestartet wurde.
+-1 = undefiniert
+0 = Fahrerkarte einlesen
+1 = Login prüfen
+2 = Login nach der Pause prüfen
+3 = Routeneingabe prüfen
+4 = Ziel prüfen
+5 = Warten auf Ticketdruck
+6 = Pause aktivieren
+7 = Abmelden</t>
+  </si>
+  <si>
+    <t>nuntius_printer_visLoadingInfo</t>
+  </si>
+  <si>
+    <t>Informationstext auf dem Ladebildschrim</t>
+  </si>
+  <si>
+    <t>nuntius_printer_ui_loadingInfo</t>
+  </si>
+  <si>
+    <t>Lade- und Fehlermeldungsinfotext</t>
+  </si>
+  <si>
+    <t>nuntius_printer_updateWaitTimer</t>
+  </si>
+  <si>
+    <t>Aktualisiert den Wartezeit-Timer für die Simulation von Ladezeiten</t>
+  </si>
+  <si>
+    <t>nuntius_printer_startWaitTime</t>
+  </si>
+  <si>
+    <t>nuntius_printer_goToPageAfterWaitTime</t>
+  </si>
+  <si>
+    <t>Öffnet die "Bitte Warten"-Seite für die Ladezeit-Simulation</t>
+  </si>
+  <si>
+    <t>Wartezeit in Sekunden</t>
+  </si>
+  <si>
+    <t>Wait-Reason für die Ladezeit</t>
+  </si>
+  <si>
+    <t>Zielseite nach Ablauf der Wartezeit</t>
+  </si>
+  <si>
+    <t>Startet die Wartezeit mit dem gegebenen Wartegrund</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1770,14 +1833,6 @@
       <color rgb="FF953800"/>
       <name val="JetBrains Mono SemiBold"/>
       <family val="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Open Sans"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1800,7 +1855,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1816,9 +1871,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2068,7 +2120,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:B114"/>
+  <dimension ref="A1:B117"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36.6640625" style="3" bestFit="1" customWidth="1"/>
@@ -2086,41 +2138,41 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="B7" s="13"/>
+      <c r="B7" s="12"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
@@ -2163,33 +2215,33 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="B15" s="13"/>
+      <c r="B15" s="12"/>
     </row>
     <row r="16" spans="1:2" ht="297" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>83</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="66" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>413</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="99" x14ac:dyDescent="0.3">
@@ -2218,10 +2270,10 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -2282,10 +2334,10 @@
     </row>
     <row r="30" spans="1:2" ht="66" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="66" x14ac:dyDescent="0.3">
@@ -2346,10 +2398,10 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -2421,497 +2473,524 @@
         <v>109</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="165" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>320</v>
+        <v>550</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="7" t="s">
-        <v>350</v>
+      <c r="A49" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
-        <v>339</v>
+      <c r="A50" t="s">
+        <v>348</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>340</v>
+        <v>554</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
-        <v>333</v>
+      <c r="A51" t="s">
+        <v>552</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>336</v>
+        <v>555</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>420</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>422</v>
-      </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>421</v>
+      <c r="A54" s="3" t="s">
+        <v>332</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>423</v>
+        <v>333</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>536</v>
+        <v>418</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>540</v>
+        <v>420</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>537</v>
+        <v>419</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>541</v>
+        <v>421</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>534</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>538</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>535</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>543</v>
-      </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59"/>
+      <c r="A59" t="s">
+        <v>536</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>540</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="15" t="s">
+      <c r="A60" t="s">
+        <v>537</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61"/>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="14" t="s">
+        <v>437</v>
+      </c>
+      <c r="B62" s="14"/>
+    </row>
+    <row r="63" spans="1:2" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A63" s="8"/>
+      <c r="B63" s="9" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="66" x14ac:dyDescent="0.3">
+      <c r="A64" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="B60" s="15"/>
-    </row>
-    <row r="61" spans="1:2" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A61" s="9"/>
-      <c r="B61" s="10" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" ht="66" x14ac:dyDescent="0.3">
-      <c r="A62" s="3" t="s">
+    </row>
+    <row r="66" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B66" s="4" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="3" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B68" s="12"/>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B69" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>425</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" ht="33" x14ac:dyDescent="0.3">
-      <c r="A64" s="3" t="s">
+      <c r="B70" s="3" t="s">
         <v>426</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="B66" s="13"/>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B67" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>427</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>127</v>
+        <v>557</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>176</v>
+        <v>558</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>315</v>
+        <v>125</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>316</v>
+        <v>174</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
-        <v>323</v>
+        <v>126</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>325</v>
+        <v>175</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>324</v>
+        <v>127</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>326</v>
+        <v>176</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>429</v>
+      <c r="A90" s="3" t="s">
+        <v>315</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>431</v>
+        <v>316</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>430</v>
+      <c r="A91" s="3" t="s">
+        <v>321</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>432</v>
+        <v>323</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>544</v>
+        <v>322</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>545</v>
+        <v>324</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93"/>
+      <c r="A93" t="s">
+        <v>427</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>429</v>
+      </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A94" s="15" t="s">
-        <v>443</v>
-      </c>
-      <c r="B94" s="15"/>
+      <c r="A94" t="s">
+        <v>428</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>433</v>
-      </c>
-      <c r="B95" s="14" t="s">
-        <v>438</v>
+      <c r="A95" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>434</v>
-      </c>
-      <c r="B96" s="14"/>
+      <c r="A96"/>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>435</v>
+      <c r="A97" s="14" t="s">
+        <v>441</v>
       </c>
       <c r="B97" s="14"/>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
+        <v>431</v>
+      </c>
+      <c r="B98" s="13" t="s">
         <v>436</v>
       </c>
-      <c r="B98" s="14"/>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>437</v>
-      </c>
-      <c r="B99" s="14"/>
+        <v>432</v>
+      </c>
+      <c r="B99" s="13"/>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>433</v>
+      </c>
+      <c r="B100" s="13"/>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A101" s="13" t="s">
-        <v>485</v>
+      <c r="A101" t="s">
+        <v>434</v>
       </c>
       <c r="B101" s="13"/>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A102" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A103" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>499</v>
-      </c>
+      <c r="A102" t="s">
+        <v>435</v>
+      </c>
+      <c r="B102" s="13"/>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A104" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="B104" t="s">
-        <v>500</v>
-      </c>
+      <c r="A104" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="B104" s="12"/>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="B105" t="s">
-        <v>501</v>
+        <v>484</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="B106" t="s">
-        <v>502</v>
+        <v>485</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="B107" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B108" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="B109" s="11" t="s">
-        <v>505</v>
+        <v>488</v>
+      </c>
+      <c r="B109" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="B110" s="14" t="s">
-        <v>507</v>
+        <v>489</v>
+      </c>
+      <c r="B110" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="B111" s="14"/>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+        <v>490</v>
+      </c>
+      <c r="B111" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="B112" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="B112" s="10" t="s">
+        <v>503</v>
+      </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="B113" s="14"/>
+        <v>491</v>
+      </c>
+      <c r="B113" s="13" t="s">
+        <v>505</v>
+      </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="B114" s="14"/>
+        <v>492</v>
+      </c>
+      <c r="B114" s="13"/>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="B115" s="13"/>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="B116" s="13"/>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B117" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A101:B101"/>
-    <mergeCell ref="B110:B114"/>
+    <mergeCell ref="A104:B104"/>
+    <mergeCell ref="B113:B117"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="B95:B99"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="B98:B102"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A97:B97"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -2921,7 +3000,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E136590C-EA4F-4E21-9125-68A5EEB7EB45}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43" style="3" customWidth="1"/>
@@ -2931,32 +3010,32 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>461</v>
+        <v>443</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="B2" s="14"/>
+        <v>444</v>
+      </c>
+      <c r="B2" s="13"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -2964,15 +3043,15 @@
         <v>180</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -2980,7 +3059,7 @@
         <v>181</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -2988,187 +3067,195 @@
         <v>182</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>183</v>
+        <v>559</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>478</v>
+        <v>560</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>454</v>
+        <v>185</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="13" t="s">
-        <v>485</v>
-      </c>
-      <c r="B29" s="13"/>
+        <v>479</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>480</v>
+      </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="B30" t="s">
-        <v>510</v>
-      </c>
+      <c r="A30" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="B30" s="12"/>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="B31" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="B32" t="s">
         <v>509</v>
-      </c>
-      <c r="B31" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="33" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="B33" s="11" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B33" s="10" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>517</v>
-      </c>
-      <c r="B34" s="11" t="s">
         <v>514</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>512</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3476,58 +3563,58 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C34" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>401</v>
+      </c>
+      <c r="C35" t="s">
         <v>403</v>
-      </c>
-      <c r="C35" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C36" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C37" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C38" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C39" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C40" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -3538,7 +3625,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{717CEF75-956F-4D6D-ADE3-21264BBAF87D}">
-  <dimension ref="A1:K117"/>
+  <dimension ref="A1:K121"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.109375" bestFit="1" customWidth="1"/>
@@ -3598,7 +3685,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -3632,10 +3719,10 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -3651,44 +3738,44 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B10" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B11" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B12" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B13" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -3744,23 +3831,23 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B25" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B26" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C26" t="s">
         <v>251</v>
@@ -3790,10 +3877,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B29" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C29" t="s">
         <v>251</v>
@@ -3801,10 +3888,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B30" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C30" t="s">
         <v>251</v>
@@ -3812,707 +3899,754 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B31" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C31" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>393</v>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>561</v>
+      </c>
+      <c r="B32" t="s">
+        <v>562</v>
+      </c>
+      <c r="C32" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>365</v>
-      </c>
-      <c r="B34" t="s">
-        <v>380</v>
+      <c r="A34" s="1" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B35" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>197</v>
+        <v>364</v>
       </c>
       <c r="B36" t="s">
-        <v>260</v>
-      </c>
-      <c r="C36" t="s">
-        <v>251</v>
+        <v>379</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>197</v>
       </c>
       <c r="B37" t="s">
-        <v>261</v>
-      </c>
-      <c r="D37" t="s">
-        <v>262</v>
+        <v>260</v>
+      </c>
+      <c r="C37" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>198</v>
+        <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>263</v>
+        <v>261</v>
+      </c>
+      <c r="D38" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>14</v>
+        <v>198</v>
       </c>
       <c r="B39" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B40" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B42" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>199</v>
+        <v>32</v>
       </c>
       <c r="B43" t="s">
-        <v>268</v>
-      </c>
-      <c r="D43" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B44" t="s">
-        <v>271</v>
+        <v>268</v>
+      </c>
+      <c r="D44" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B45" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B46" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B47" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>327</v>
+        <v>203</v>
       </c>
       <c r="B48" t="s">
-        <v>329</v>
+        <v>273</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B49" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="B50" t="s">
-        <v>358</v>
+        <v>328</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="B51" t="s">
-        <v>274</v>
+        <v>356</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B52" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B53" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>101</v>
+        <v>206</v>
       </c>
       <c r="B54" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>207</v>
+        <v>101</v>
       </c>
       <c r="B55" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B56" t="s">
-        <v>279</v>
-      </c>
-      <c r="D56" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B57" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D57" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B58" t="s">
-        <v>283</v>
+        <v>281</v>
+      </c>
+      <c r="D58" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>210</v>
+      </c>
+      <c r="B59" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>211</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B60" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="33" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+    <row r="61" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>212</v>
       </c>
-      <c r="B60" s="11" t="s">
-        <v>547</v>
-      </c>
-      <c r="C60" t="s">
+      <c r="B61" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="C61" t="s">
         <v>251</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>213</v>
-      </c>
-      <c r="B61" t="s">
-        <v>285</v>
-      </c>
-      <c r="D61" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>312</v>
+        <v>213</v>
       </c>
       <c r="B62" t="s">
-        <v>313</v>
+        <v>285</v>
       </c>
       <c r="D62" t="s">
-        <v>314</v>
+        <v>286</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>214</v>
+        <v>312</v>
       </c>
       <c r="B63" t="s">
-        <v>287</v>
+        <v>313</v>
+      </c>
+      <c r="D63" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B65" t="s">
-        <v>534</v>
-      </c>
-      <c r="D65" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>309</v>
+        <v>216</v>
       </c>
       <c r="B66" t="s">
-        <v>535</v>
+        <v>532</v>
+      </c>
+      <c r="D66" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>530</v>
+        <v>309</v>
       </c>
       <c r="B67" t="s">
         <v>533</v>
       </c>
-      <c r="D67" t="s">
-        <v>532</v>
-      </c>
-      <c r="E67" t="s">
-        <v>531</v>
-      </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>217</v>
+        <v>528</v>
       </c>
       <c r="B68" t="s">
-        <v>289</v>
+        <v>531</v>
+      </c>
+      <c r="D68" t="s">
+        <v>530</v>
+      </c>
+      <c r="E68" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B69" t="s">
-        <v>291</v>
-      </c>
-      <c r="D69" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>310</v>
+        <v>218</v>
       </c>
       <c r="B70" t="s">
-        <v>311</v>
+        <v>291</v>
+      </c>
+      <c r="D70" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>548</v>
+        <v>310</v>
       </c>
       <c r="B71" t="s">
-        <v>550</v>
+        <v>311</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B72" t="s">
-        <v>551</v>
-      </c>
-      <c r="C72" t="s">
-        <v>251</v>
+        <v>548</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>219</v>
+        <v>547</v>
       </c>
       <c r="B73" t="s">
-        <v>292</v>
+        <v>549</v>
+      </c>
+      <c r="C73" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B74" t="s">
-        <v>293</v>
-      </c>
-      <c r="D74" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B75" t="s">
-        <v>295</v>
+        <v>293</v>
+      </c>
+      <c r="D75" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B76" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B77" t="s">
-        <v>297</v>
-      </c>
-      <c r="D77" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B78" t="s">
-        <v>299</v>
-      </c>
-      <c r="C78" t="s">
-        <v>251</v>
+        <v>297</v>
+      </c>
+      <c r="D78" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B79" t="s">
-        <v>300</v>
+        <v>299</v>
+      </c>
+      <c r="C79" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>225</v>
+      </c>
+      <c r="B80" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>564</v>
+      </c>
+      <c r="B81" t="s">
+        <v>565</v>
+      </c>
+      <c r="D81" t="s">
+        <v>566</v>
+      </c>
+      <c r="E81" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>563</v>
+      </c>
+      <c r="B82" t="s">
+        <v>569</v>
+      </c>
+      <c r="D82" t="s">
+        <v>566</v>
+      </c>
+      <c r="E82" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>226</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B83" t="s">
         <v>301</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D83" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>227</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B84" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="1" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
         <v>228</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B87" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>367</v>
-      </c>
-      <c r="B85" s="14" t="s">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>365</v>
+      </c>
+      <c r="B88" s="13" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+      <c r="D88" s="13" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
         <v>229</v>
       </c>
-      <c r="B86" s="14"/>
-      <c r="D86" s="14" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+      <c r="B89" s="13"/>
+      <c r="D89" s="13"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
         <v>230</v>
       </c>
-      <c r="B87" s="14"/>
-      <c r="D87" s="14"/>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+      <c r="B90" s="13"/>
+      <c r="D90" s="13"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
         <v>231</v>
       </c>
-      <c r="B88" s="14"/>
-      <c r="D88" s="14"/>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+      <c r="B91" s="13"/>
+      <c r="D91" s="13"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
         <v>232</v>
       </c>
-      <c r="B89" s="14"/>
-      <c r="D89" s="14"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+      <c r="B92" s="13"/>
+      <c r="D92" s="13"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
         <v>233</v>
       </c>
-      <c r="B90" s="14"/>
-      <c r="D90" s="14"/>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+      <c r="B93" s="13"/>
+      <c r="D93" s="13"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
         <v>234</v>
       </c>
-      <c r="B91" s="14"/>
-      <c r="D91" s="14"/>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+      <c r="B94" s="13"/>
+      <c r="D94" s="13"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
         <v>235</v>
       </c>
-      <c r="B92" s="14"/>
-      <c r="D92" s="14"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>236</v>
-      </c>
-      <c r="B93" s="14"/>
-      <c r="D93" s="14"/>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>237</v>
-      </c>
-      <c r="B94" s="14"/>
-      <c r="D94" s="14"/>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>238</v>
-      </c>
-      <c r="B95" s="14"/>
-      <c r="D95" s="14"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B95" s="13"/>
+      <c r="D95" s="13"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>239</v>
-      </c>
-      <c r="B96" s="14"/>
-      <c r="D96" s="14"/>
+        <v>557</v>
+      </c>
+      <c r="B96" s="13"/>
+      <c r="D96" s="13"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>240</v>
-      </c>
-      <c r="B97" s="14"/>
-      <c r="D97" s="14"/>
+        <v>236</v>
+      </c>
+      <c r="B97" s="13"/>
+      <c r="D97" s="13"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>241</v>
-      </c>
-      <c r="B98" s="14"/>
-      <c r="D98" s="14"/>
+        <v>237</v>
+      </c>
+      <c r="B98" s="13"/>
+      <c r="D98" s="13"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>242</v>
-      </c>
-      <c r="B99" s="14"/>
-      <c r="D99" s="14"/>
+        <v>238</v>
+      </c>
+      <c r="B99" s="13"/>
+      <c r="D99" s="13"/>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>243</v>
-      </c>
-      <c r="B100" s="14"/>
-      <c r="D100" s="14"/>
+        <v>239</v>
+      </c>
+      <c r="B100" s="13"/>
+      <c r="D100" s="13"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>244</v>
-      </c>
-      <c r="B101" s="14"/>
-      <c r="D101" s="14"/>
+        <v>240</v>
+      </c>
+      <c r="B101" s="13"/>
+      <c r="D101" s="13"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>354</v>
-      </c>
-      <c r="B102" s="14"/>
-      <c r="D102" s="14"/>
+        <v>241</v>
+      </c>
+      <c r="B102" s="13"/>
+      <c r="D102" s="13"/>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>355</v>
-      </c>
-      <c r="B103" s="14"/>
-      <c r="D103" s="14"/>
+        <v>242</v>
+      </c>
+      <c r="B103" s="13"/>
+      <c r="D103" s="13"/>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>356</v>
-      </c>
-      <c r="B104" s="14"/>
-      <c r="D104" s="14"/>
+        <v>243</v>
+      </c>
+      <c r="B104" s="13"/>
+      <c r="D104" s="13"/>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>368</v>
-      </c>
-      <c r="B105" s="8"/>
-      <c r="D105" s="8"/>
+        <v>244</v>
+      </c>
+      <c r="B105" s="13"/>
+      <c r="D105" s="13"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>369</v>
-      </c>
-      <c r="B106" s="8"/>
-      <c r="D106" s="8"/>
+        <v>352</v>
+      </c>
+      <c r="B106" s="13"/>
+      <c r="D106" s="13"/>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B107" s="5"/>
-      <c r="D107" s="5"/>
+      <c r="A107" t="s">
+        <v>353</v>
+      </c>
+      <c r="B107" s="13"/>
+      <c r="D107" s="13"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="B108" s="8"/>
-      <c r="D108" s="8"/>
+      <c r="A108" t="s">
+        <v>354</v>
+      </c>
+      <c r="B108" s="13"/>
+      <c r="D108" s="13"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>245</v>
-      </c>
-      <c r="B109" t="s">
-        <v>307</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="B109" s="13"/>
+      <c r="D109" s="13"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>246</v>
-      </c>
-      <c r="B110" t="s">
-        <v>308</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="B110" s="13"/>
+      <c r="D110" s="13"/>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>370</v>
-      </c>
-      <c r="B111" t="s">
-        <v>382</v>
-      </c>
+      <c r="B111" s="5"/>
+      <c r="D111" s="5"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B112" s="7"/>
+      <c r="D112" s="7"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" s="1" t="s">
-        <v>396</v>
+      <c r="A113" t="s">
+        <v>245</v>
+      </c>
+      <c r="B113" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>371</v>
+        <v>246</v>
       </c>
       <c r="B114" t="s">
-        <v>383</v>
-      </c>
-      <c r="D114" t="s">
-        <v>384</v>
-      </c>
-      <c r="E114" t="s">
-        <v>385</v>
+        <v>308</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
+        <v>368</v>
+      </c>
+      <c r="B115" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>369</v>
+      </c>
+      <c r="B118" t="s">
+        <v>381</v>
+      </c>
+      <c r="D118" t="s">
+        <v>382</v>
+      </c>
+      <c r="E118" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>370</v>
+      </c>
+      <c r="B119" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>371</v>
+      </c>
+      <c r="B120" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
         <v>372</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B121" t="s">
         <v>386</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>373</v>
-      </c>
-      <c r="B116" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>374</v>
-      </c>
-      <c r="B117" t="s">
-        <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="D86:D104"/>
-    <mergeCell ref="B85:B104"/>
+    <mergeCell ref="B88:B110"/>
+    <mergeCell ref="D88:D110"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -4529,43 +4663,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
+        <v>516</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>518</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
         <v>520</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
         <v>524</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>525</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
-        <v>526</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>527</v>
       </c>
     </row>
   </sheetData>

--- a/Dokumentation.xlsx
+++ b/Dokumentation.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20401"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C7948D-C147-4174-925D-2BD46F6A681E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E9BA63-8698-4BBC-948A-A38E6B6A3155}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variablen" sheetId="2" r:id="rId1"/>
@@ -1757,6 +1757,45 @@
     <t>Ziel-Page nach Ablauf der Wartezeit</t>
   </si>
   <si>
+    <t>nuntius_printer_visLoadingInfo</t>
+  </si>
+  <si>
+    <t>Informationstext auf dem Ladebildschrim</t>
+  </si>
+  <si>
+    <t>nuntius_printer_ui_loadingInfo</t>
+  </si>
+  <si>
+    <t>Lade- und Fehlermeldungsinfotext</t>
+  </si>
+  <si>
+    <t>nuntius_printer_updateWaitTimer</t>
+  </si>
+  <si>
+    <t>Aktualisiert den Wartezeit-Timer für die Simulation von Ladezeiten</t>
+  </si>
+  <si>
+    <t>nuntius_printer_startWaitTime</t>
+  </si>
+  <si>
+    <t>nuntius_printer_goToPageAfterWaitTime</t>
+  </si>
+  <si>
+    <t>Öffnet die "Bitte Warten"-Seite für die Ladezeit-Simulation</t>
+  </si>
+  <si>
+    <t>Wartezeit in Sekunden</t>
+  </si>
+  <si>
+    <t>Wait-Reason für die Ladezeit</t>
+  </si>
+  <si>
+    <t>Zielseite nach Ablauf der Wartezeit</t>
+  </si>
+  <si>
+    <t>Startet die Wartezeit mit dem gegebenen Wartegrund</t>
+  </si>
+  <si>
     <t>Enum-Wert für den Grund der Wartezeit, die gestartet wurde.
 -1 = undefiniert
 0 = Fahrerkarte einlesen
@@ -1766,46 +1805,8 @@
 4 = Ziel prüfen
 5 = Warten auf Ticketdruck
 6 = Pause aktivieren
-7 = Abmelden</t>
-  </si>
-  <si>
-    <t>nuntius_printer_visLoadingInfo</t>
-  </si>
-  <si>
-    <t>Informationstext auf dem Ladebildschrim</t>
-  </si>
-  <si>
-    <t>nuntius_printer_ui_loadingInfo</t>
-  </si>
-  <si>
-    <t>Lade- und Fehlermeldungsinfotext</t>
-  </si>
-  <si>
-    <t>nuntius_printer_updateWaitTimer</t>
-  </si>
-  <si>
-    <t>Aktualisiert den Wartezeit-Timer für die Simulation von Ladezeiten</t>
-  </si>
-  <si>
-    <t>nuntius_printer_startWaitTime</t>
-  </si>
-  <si>
-    <t>nuntius_printer_goToPageAfterWaitTime</t>
-  </si>
-  <si>
-    <t>Öffnet die "Bitte Warten"-Seite für die Ladezeit-Simulation</t>
-  </si>
-  <si>
-    <t>Wartezeit in Sekunden</t>
-  </si>
-  <si>
-    <t>Wait-Reason für die Ladezeit</t>
-  </si>
-  <si>
-    <t>Zielseite nach Ablauf der Wartezeit</t>
-  </si>
-  <si>
-    <t>Startet die Wartezeit mit dem gegebenen Wartegrund</t>
+7 = Abmelden
+10 = Fahrerkarte nach der Pause einlesen</t>
   </si>
 </sst>
 </file>
@@ -2476,12 +2477,12 @@
         <v>350</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="165" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" ht="181.5" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>550</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>556</v>
+        <v>569</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -2760,10 +2761,10 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>557</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
@@ -3160,10 +3161,10 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>559</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -3910,10 +3911,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>560</v>
+      </c>
+      <c r="B32" t="s">
         <v>561</v>
-      </c>
-      <c r="B32" t="s">
-        <v>562</v>
       </c>
       <c r="C32" t="s">
         <v>251</v>
@@ -4342,30 +4343,30 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>563</v>
+      </c>
+      <c r="B81" t="s">
         <v>564</v>
       </c>
-      <c r="B81" t="s">
+      <c r="D81" t="s">
         <v>565</v>
       </c>
-      <c r="D81" t="s">
-        <v>566</v>
-      </c>
       <c r="E81" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B82" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D82" t="s">
+        <v>565</v>
+      </c>
+      <c r="E82" t="s">
         <v>566</v>
-      </c>
-      <c r="E82" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -4462,7 +4463,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B96" s="13"/>
       <c r="D96" s="13"/>
